--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-encounter.xlsx
@@ -566,7 +566,7 @@
     <t>過去のEncounterのステータス一覧【詳細参照】</t>
   </si>
   <si>
-    <t>ステータス履歴(status History)は、リソースの歴史的なバージョンを読み込んだり、サーバに保存させたりすることなく、Encounterリソースがステータス履歴を含むことを可能にする。</t>
+    <t>ステータス履歴(status History)は、リソースの歴史的なバージョンを読み込んだり、サーバーに保存させたりすることなく、Encounterリソースがステータス履歴を含むことを可能にする。</t>
   </si>
   <si>
     <t>現在のステータスは、ステータスの履歴ではなく、常にリソースの現在のバージョンにある。</t>
